--- a/hall/resources/sample/shop.xlsx
+++ b/hall/resources/sample/shop.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gamedoc\游戏配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\hall\resources\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF3D3DE-B55D-4105-BD4F-BF620C8AC67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58125795-6A91-4C3D-826F-5D49B0FF930F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34320" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ShopConfig" sheetId="1" r:id="rId1"/>
+    <sheet name="Shop" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/hall/resources/sample/shop.xlsx
+++ b/hall/resources/sample/shop.xlsx
@@ -1,77 +1,82 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gameserver\hall\resources\sample\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58125795-6A91-4C3D-826F-5D49B0FF930F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34320" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Shop" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
-  <si>
-    <t>sid</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
+  <si>
+    <t>id</t>
   </si>
   <si>
     <t>名称</t>
   </si>
   <si>
+    <t>图标</t>
+  </si>
+  <si>
+    <t>标签</t>
+  </si>
+  <si>
+    <t>道具奖励</t>
+  </si>
+  <si>
+    <t>购买价格</t>
+  </si>
+  <si>
+    <t>分类</t>
+  </si>
+  <si>
+    <t>天数规则</t>
+  </si>
+  <si>
+    <t>等级条件</t>
+  </si>
+  <si>
+    <t>指定日期开放</t>
+  </si>
+  <si>
+    <t>存在时间</t>
+  </si>
+  <si>
+    <t>折扣原价</t>
+  </si>
+  <si>
+    <t>折扣</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
+    <t>String</t>
+  </si>
+  <si>
     <t>name</t>
   </si>
   <si>
-    <t>图标</t>
-  </si>
-  <si>
-    <t>标签</t>
-  </si>
-  <si>
-    <t>道具奖励</t>
-  </si>
-  <si>
-    <t>购买价格</t>
-  </si>
-  <si>
-    <t>分类</t>
-  </si>
-  <si>
-    <t>天数规则</t>
-  </si>
-  <si>
-    <t>等级条件</t>
-  </si>
-  <si>
-    <t>指定日期开放</t>
-  </si>
-  <si>
-    <t>存在时间</t>
-  </si>
-  <si>
-    <t>折扣原价</t>
-  </si>
-  <si>
-    <t>折扣</t>
-  </si>
-  <si>
     <t>icon1</t>
   </si>
   <si>
@@ -103,28 +108,23 @@
   </si>
   <si>
     <t>discountratio</t>
-  </si>
-  <si>
-    <t>String</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -132,20 +132,356 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -168,9 +504,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -180,24 +758,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -246,7 +868,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -281,7 +903,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -455,19 +1077,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
   <cols>
     <col min="2" max="2" width="16.625" customWidth="1"/>
     <col min="3" max="3" width="15.25" customWidth="1"/>
@@ -482,7 +1099,7 @@
     <col min="13" max="13" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -490,120 +1107,122 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="L3" s="3" t="s">
         <v>25</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/hall/resources/sample/shop.xlsx
+++ b/hall/resources/sample/shop.xlsx
@@ -1,38 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\gamedoc\游戏配置表\common\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{244EA50E-E727-4F08-98A4-270F738E559D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="ShopConfig" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -41,7 +47,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -51,14 +56,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -67,26 +71,21 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-条件：角色等级_值、VIP等级_值：
-1. 角色等级；
-2. VIP等级；
-达到设定等级该礼包可见，反之 不可见
-注：这两个条件可以同时存在，即都满足才可见</t>
+条件配置表类型_值
+注：当有多个条件时，即都满足才可见</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -95,7 +94,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -105,14 +103,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -121,7 +118,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -129,14 +125,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -145,7 +140,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -153,14 +147,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -169,7 +162,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -178,14 +170,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -194,7 +185,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -202,14 +192,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -218,7 +207,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -226,14 +214,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -242,7 +229,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -250,14 +236,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -266,7 +251,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -275,14 +259,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -291,7 +274,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -299,14 +281,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="O5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="O5" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -315,7 +296,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -323,14 +303,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="O8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+    <comment ref="O8" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -339,7 +318,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -408,12 +386,15 @@
     <t>bool</t>
   </si>
   <si>
+    <t>Date&lt;yyyy-MM-dd HH:mm:ss&gt;</t>
+  </si>
+  <si>
+    <t>map&lt;int{_}long&gt;{;}</t>
+  </si>
+  <si>
     <t>String</t>
   </si>
   <si>
-    <t>map&lt;int{_}long&gt;{;}</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -456,7 +437,7 @@
     <t>热卖</t>
   </si>
   <si>
-    <t>1_10;2_4</t>
+    <t>1_10</t>
   </si>
   <si>
     <t>1022503_10</t>
@@ -474,6 +455,12 @@
     <t>1_5</t>
   </si>
   <si>
+    <t>2025-9-17 00:00:00</t>
+  </si>
+  <si>
+    <t>2025-9-25 23:59:59</t>
+  </si>
+  <si>
     <t>1022503_5</t>
   </si>
   <si>
@@ -492,6 +479,9 @@
     <t>1_1</t>
   </si>
   <si>
+    <t>2025-9-30 23:59:59</t>
+  </si>
+  <si>
     <t>1022503_1</t>
   </si>
   <si>
@@ -604,29 +594,19 @@
   </si>
   <si>
     <t>1980000_1000</t>
-  </si>
-  <si>
-    <t>Date&lt;yyyy-MM-dd HH:mm:ss&gt;</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-9-17 00:00:00</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-9-30 23:59:59</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025-9-25 23:59:59</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -638,45 +618,177 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -685,30 +797,228 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -731,11 +1041,253 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -754,33 +1306,79 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1038,14 +1636,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="5.5" style="1" customWidth="1"/>
@@ -1063,7 +1661,7 @@
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1110,7 +1708,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15">
       <c r="A2" s="5" t="s">
         <v>15</v>
       </c>
@@ -1125,80 +1723,80 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>84</v>
+      <c r="G2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="20" t="s">
         <v>15</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N2" s="5" t="s">
         <v>15</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15">
       <c r="A5" s="9">
         <v>1001</v>
       </c>
@@ -1206,11 +1804,11 @@
         <v>1</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" s="9" t="b">
         <v>1</v>
@@ -1218,24 +1816,24 @@
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
       <c r="I5" s="9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
       <c r="L5" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N5" s="9">
         <v>100</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15">
       <c r="A6" s="9">
         <v>1002</v>
       </c>
@@ -1243,44 +1841,44 @@
         <v>1</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F6" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G6" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>87</v>
+      <c r="G6" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N6" s="9">
         <v>50</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15">
       <c r="A7" s="9">
         <v>1003</v>
       </c>
@@ -1288,521 +1886,521 @@
         <v>1</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F7" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G7" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>86</v>
+      <c r="G7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
       <c r="O7" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="12">
+        <v>2001</v>
+      </c>
+      <c r="B8" s="12">
+        <v>2</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="M8" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="N8" s="12">
+        <v>100</v>
+      </c>
+      <c r="O8" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="12">
+        <v>2002</v>
+      </c>
+      <c r="B9" s="12">
+        <v>2</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="M9" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="N9" s="12">
+        <v>100</v>
+      </c>
+      <c r="O9" s="12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="12">
+        <v>2003</v>
+      </c>
+      <c r="B10" s="12">
+        <v>2</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L10" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="N10" s="12">
+        <v>100</v>
+      </c>
+      <c r="O10" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="12">
+        <v>2004</v>
+      </c>
+      <c r="B11" s="12">
+        <v>2</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="15" t="s">
         <v>49</v>
       </c>
+      <c r="I11" s="12"/>
+      <c r="J11" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" s="14">
+        <v>4999</v>
+      </c>
+      <c r="M11" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="N11" s="12">
+        <v>100</v>
+      </c>
+      <c r="O11" s="12" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="11">
-        <v>2001</v>
-      </c>
-      <c r="B8" s="11">
+    <row r="12" spans="1:15">
+      <c r="A12" s="12">
+        <v>2005</v>
+      </c>
+      <c r="B12" s="12">
         <v>2</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C12" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="L12" s="14">
+        <v>1999</v>
+      </c>
+      <c r="M12" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="N12" s="12">
+        <v>100</v>
+      </c>
+      <c r="O12" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="12">
+        <v>2006</v>
+      </c>
+      <c r="B13" s="12">
+        <v>2</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="L13" s="14">
+        <v>499</v>
+      </c>
+      <c r="M13" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="N13" s="12">
         <v>50</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="9" t="b">
+      <c r="O13" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="16">
+        <v>3001</v>
+      </c>
+      <c r="B14" s="16">
+        <v>3</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="17" t="b">
         <v>1</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="K8" s="12" t="s">
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="L14" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N14" s="16">
+        <v>100</v>
+      </c>
+      <c r="O14" s="16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="16">
+        <v>3002</v>
+      </c>
+      <c r="B15" s="16">
+        <v>3</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="L15" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N15" s="16">
+        <v>50</v>
+      </c>
+      <c r="O15" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="16">
+        <v>3003</v>
+      </c>
+      <c r="B16" s="16">
+        <v>3</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="J16" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="K16" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="L16" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N16" s="16">
+        <v>50</v>
+      </c>
+      <c r="O16" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="16">
+        <v>3004</v>
+      </c>
+      <c r="B17" s="16">
+        <v>3</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" s="16"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="L17" s="18">
+        <v>4999</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="16">
+        <v>3005</v>
+      </c>
+      <c r="B18" s="16">
+        <v>3</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="L18" s="18">
+        <v>1999</v>
+      </c>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="16">
+        <v>3006</v>
+      </c>
+      <c r="B19" s="16">
+        <v>3</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="L19" s="18">
+        <v>499</v>
+      </c>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16" t="s">
         <v>53</v>
-      </c>
-      <c r="L8" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="N8" s="11">
-        <v>100</v>
-      </c>
-      <c r="O8" s="11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="11">
-        <v>2002</v>
-      </c>
-      <c r="B9" s="11">
-        <v>2</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="J9" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="K9" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="L9" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="N9" s="11">
-        <v>100</v>
-      </c>
-      <c r="O9" s="11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="11">
-        <v>2003</v>
-      </c>
-      <c r="B10" s="11">
-        <v>2</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="N10" s="11">
-        <v>100</v>
-      </c>
-      <c r="O10" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="11">
-        <v>2004</v>
-      </c>
-      <c r="B11" s="11">
-        <v>2</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="K11" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="L11" s="12">
-        <v>4999</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="N11" s="11">
-        <v>100</v>
-      </c>
-      <c r="O11" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="11">
-        <v>2005</v>
-      </c>
-      <c r="B12" s="11">
-        <v>2</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="K12" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="L12" s="12">
-        <v>1999</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="N12" s="11">
-        <v>100</v>
-      </c>
-      <c r="O12" s="11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="11">
-        <v>2006</v>
-      </c>
-      <c r="B13" s="11">
-        <v>2</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="L13" s="12">
-        <v>499</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="N13" s="11">
-        <v>50</v>
-      </c>
-      <c r="O13" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="13">
-        <v>3001</v>
-      </c>
-      <c r="B14" s="13">
-        <v>3</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="K14" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="N14" s="13">
-        <v>100</v>
-      </c>
-      <c r="O14" s="13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="13">
-        <v>3002</v>
-      </c>
-      <c r="B15" s="13">
-        <v>3</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="K15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="N15" s="13">
-        <v>50</v>
-      </c>
-      <c r="O15" s="13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="13">
-        <v>3003</v>
-      </c>
-      <c r="B16" s="13">
-        <v>3</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="L16" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="M16" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="N16" s="13">
-        <v>50</v>
-      </c>
-      <c r="O16" s="13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="13">
-        <v>3004</v>
-      </c>
-      <c r="B17" s="13">
-        <v>3</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="I17" s="13"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="L17" s="14">
-        <v>4999</v>
-      </c>
-      <c r="M17" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="13">
-        <v>3005</v>
-      </c>
-      <c r="B18" s="13">
-        <v>3</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="L18" s="14">
-        <v>1999</v>
-      </c>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="13">
-        <v>3006</v>
-      </c>
-      <c r="B19" s="13">
-        <v>3</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="F19" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="L19" s="14">
-        <v>499</v>
-      </c>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13" t="s">
-        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/shop.xlsx
+++ b/hall/resources/sample/shop.xlsx
@@ -165,8 +165,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-购买成功获得道具数量
-</t>
+购买成功获得道具数量：
+金币充值和钻石充值 仅配置 金币和钻石，不配置其它道具 UI不支持</t>
         </r>
       </text>
     </comment>
@@ -188,7 +188,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-仅显示用</t>
+仅显示用：用在金币和钻石充值；其它类型不配置 UI暂不支持</t>
         </r>
       </text>
     </comment>
@@ -210,7 +210,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-购买成功获得货币数量</t>
+值=-1：充值类
+值&gt;-1：兑换类</t>
         </r>
       </text>
     </comment>
@@ -330,7 +331,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="85">
   <si>
     <t>id</t>
   </si>
@@ -359,10 +360,10 @@
     <t>道具奖励</t>
   </si>
   <si>
-    <t>金币或钻石原价数量</t>
-  </si>
-  <si>
-    <t>金币或钻石售价数量</t>
+    <t>原价值</t>
+  </si>
+  <si>
+    <t>购买类型</t>
   </si>
   <si>
     <t>购买价格</t>
@@ -419,7 +420,7 @@
     <t>discount</t>
   </si>
   <si>
-    <t>discountratio</t>
+    <t>paytype</t>
   </si>
   <si>
     <t>money</t>
@@ -443,7 +444,7 @@
     <t>1022503_10</t>
   </si>
   <si>
-    <t>999</t>
+    <t>200</t>
   </si>
   <si>
     <t>sc_best value.png</t>
@@ -464,136 +465,127 @@
     <t>1022503_5</t>
   </si>
   <si>
+    <t>-1</t>
+  </si>
+  <si>
+    <t>499</t>
+  </si>
+  <si>
+    <t>sc_zhuanshi_icon6.png</t>
+  </si>
+  <si>
+    <t>1_1</t>
+  </si>
+  <si>
+    <t>2025-9-30 23:59:59</t>
+  </si>
+  <si>
+    <t>1022503_1</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>sc_zhuanshi_icon1.png</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>1990000_20000000</t>
+  </si>
+  <si>
+    <t>1990000_10000000</t>
+  </si>
+  <si>
+    <t>29999</t>
+  </si>
+  <si>
+    <t>1990000_16000000</t>
+  </si>
+  <si>
+    <t>1990000_8000000</t>
+  </si>
+  <si>
+    <t>12999</t>
+  </si>
+  <si>
+    <t>sc_jinbi_icon5.png</t>
+  </si>
+  <si>
+    <t>1990000_12000000</t>
+  </si>
+  <si>
+    <t>1990000_6000000</t>
+  </si>
+  <si>
+    <t>9999</t>
+  </si>
+  <si>
+    <t>sc_jinbi_icon4.png</t>
+  </si>
+  <si>
+    <t>1990000_5000000</t>
+  </si>
+  <si>
+    <t>sc_jinbi_icon3.png</t>
+  </si>
+  <si>
+    <t>1990000_4000000</t>
+  </si>
+  <si>
+    <t>sc_jinbi_icon2.png</t>
+  </si>
+  <si>
     <t>1990000_2000000</t>
   </si>
   <si>
-    <t>1990000_3000000</t>
-  </si>
-  <si>
-    <t>499</t>
-  </si>
-  <si>
-    <t>sc_zhuanshi_icon6.png</t>
-  </si>
-  <si>
-    <t>1_1</t>
-  </si>
-  <si>
-    <t>2025-9-30 23:59:59</t>
-  </si>
-  <si>
-    <t>1022503_1</t>
-  </si>
-  <si>
-    <t>1990000_1500000</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>sc_zhuanshi_icon1.png</t>
-  </si>
-  <si>
-    <t>金币</t>
-  </si>
-  <si>
-    <t>1022503_30</t>
-  </si>
-  <si>
-    <t>1990000_10000000</t>
-  </si>
-  <si>
-    <t>1990000_20000000</t>
-  </si>
-  <si>
-    <t>29999</t>
-  </si>
-  <si>
-    <t>1022503_20</t>
-  </si>
-  <si>
-    <t>1990000_8000000</t>
-  </si>
-  <si>
-    <t>1990000_16000000</t>
-  </si>
-  <si>
-    <t>12999</t>
-  </si>
-  <si>
-    <t>sc_jinbi_icon5.png</t>
-  </si>
-  <si>
-    <t>1990000_6000000</t>
-  </si>
-  <si>
-    <t>1990000_12000000</t>
-  </si>
-  <si>
-    <t>9999</t>
-  </si>
-  <si>
-    <t>sc_jinbi_icon4.png</t>
-  </si>
-  <si>
-    <t>1990000_5000000</t>
-  </si>
-  <si>
-    <t>sc_jinbi_icon3.png</t>
-  </si>
-  <si>
-    <t>1990000_4000000</t>
-  </si>
-  <si>
-    <t>sc_jinbi_icon2.png</t>
-  </si>
-  <si>
     <t>sc_jinbi_icon1.png</t>
   </si>
   <si>
     <t>钻石</t>
   </si>
   <si>
+    <t>1980000_20000</t>
+  </si>
+  <si>
     <t>1980000_10000</t>
   </si>
   <si>
-    <t>1980000_20000</t>
-  </si>
-  <si>
     <t>sc_most popular.png</t>
   </si>
   <si>
+    <t>1980000_12000</t>
+  </si>
+  <si>
     <t>1980000_8000</t>
   </si>
   <si>
-    <t>1980000_12000</t>
-  </si>
-  <si>
     <t>sc_zhuanshi_icon5.png</t>
   </si>
   <si>
+    <t>1980000_9000</t>
+  </si>
+  <si>
     <t>1980000_6000</t>
   </si>
   <si>
-    <t>1980000_9000</t>
-  </si>
-  <si>
     <t>sc_zhuanshi_icon4.png</t>
   </si>
   <si>
-    <t>1980000_4000</t>
+    <t>1990000_5000</t>
   </si>
   <si>
     <t>sc_zhuanshi_icon3.png</t>
   </si>
   <si>
-    <t>1980000_2000</t>
+    <t>1990000_3000</t>
   </si>
   <si>
     <t>sc_zhuanshi_icon2.png</t>
   </si>
   <si>
-    <t>1980000_1000</t>
+    <t>1990000_1000</t>
   </si>
 </sst>
 </file>
@@ -606,7 +598,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -622,12 +614,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -777,18 +763,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -881,12 +867,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -911,12 +891,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -953,12 +927,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -996,12 +964,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1157,82 +1119,88 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1241,53 +1209,47 @@
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1306,23 +1268,17 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1653,7 +1609,8 @@
     <col min="7" max="7" width="30.25" style="2" customWidth="1"/>
     <col min="8" max="8" width="28.25" style="2" customWidth="1"/>
     <col min="9" max="9" width="19.5" style="1" customWidth="1"/>
-    <col min="10" max="11" width="20.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20.125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9.25" style="2" customWidth="1"/>
     <col min="12" max="12" width="8.875" style="2" customWidth="1"/>
     <col min="13" max="13" width="21.625" style="1" customWidth="1"/>
     <col min="14" max="14" width="6.875" style="1" customWidth="1"/>
@@ -1732,13 +1689,13 @@
       <c r="I2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="20" t="s">
+      <c r="K2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>15</v>
       </c>
       <c r="M2" s="5" t="s">
@@ -1819,7 +1776,9 @@
         <v>36</v>
       </c>
       <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
+      <c r="K5" s="10">
+        <v>1980000</v>
+      </c>
       <c r="L5" s="10" t="s">
         <v>37</v>
       </c>
@@ -1850,23 +1809,21 @@
       <c r="F6" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="10" t="s">
         <v>42</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="10"/>
+      <c r="K6" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="L6" s="10" t="s">
         <v>45</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>46</v>
       </c>
       <c r="M6" s="9" t="s">
         <v>38</v>
@@ -1875,7 +1832,7 @@
         <v>50</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1890,511 +1847,523 @@
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F7" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>49</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>50</v>
       </c>
       <c r="J7" s="10"/>
       <c r="K7" s="10" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
       <c r="O7" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="12">
+      <c r="A8" s="11">
         <v>2001</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <v>2</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="J8" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="12" t="s">
+      <c r="K8" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="N8" s="12">
+      <c r="N8" s="11">
         <v>100</v>
       </c>
-      <c r="O8" s="12" t="s">
+      <c r="O8" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="12">
+      <c r="A9" s="11">
         <v>2002</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <v>2</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="13" t="b">
+      <c r="C9" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="12" t="s">
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N9" s="11">
+        <v>100</v>
+      </c>
+      <c r="O9" s="11" t="s">
         <v>59</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="M9" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="N9" s="12">
-        <v>100</v>
-      </c>
-      <c r="O9" s="12" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="12">
+      <c r="A10" s="11">
         <v>2003</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <v>2</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="13" t="b">
+      <c r="C10" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="M10" s="12" t="s">
+      <c r="I10" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="M10" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="N10" s="12">
+      <c r="N10" s="11">
         <v>100</v>
       </c>
-      <c r="O10" s="12" t="s">
-        <v>67</v>
+      <c r="O10" s="11" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="12">
+      <c r="A11" s="11">
         <v>2004</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>2</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="L11" s="14">
+      <c r="J11" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="L11" s="13">
         <v>4999</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="N11" s="12">
+      <c r="N11" s="11">
         <v>100</v>
       </c>
-      <c r="O11" s="12" t="s">
-        <v>69</v>
+      <c r="O11" s="11" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="12">
+      <c r="A12" s="11">
         <v>2005</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <v>2</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="13" t="b">
+      <c r="C12" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="K12" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="L12" s="14">
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="L12" s="13">
         <v>1999</v>
       </c>
-      <c r="M12" s="12" t="s">
+      <c r="M12" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="N12" s="12">
+      <c r="N12" s="11">
         <v>100</v>
       </c>
-      <c r="O12" s="12" t="s">
-        <v>71</v>
+      <c r="O12" s="11" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="12">
+      <c r="A13" s="11">
         <v>2006</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <v>2</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="13" t="b">
+      <c r="C13" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="14" t="s">
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="K13" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="L13" s="14">
+      <c r="L13" s="13">
         <v>499</v>
       </c>
-      <c r="M13" s="12" t="s">
+      <c r="M13" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="N13" s="12">
-        <v>50</v>
-      </c>
-      <c r="O13" s="12" t="s">
-        <v>72</v>
+      <c r="N13" s="11">
+        <v>100</v>
+      </c>
+      <c r="O13" s="11" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="16">
+      <c r="A14" s="14">
         <v>3001</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="14">
         <v>3</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M14" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="L14" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="M14" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="N14" s="16">
+      <c r="N14" s="14">
         <v>100</v>
       </c>
-      <c r="O14" s="16" t="s">
-        <v>47</v>
+      <c r="O14" s="14" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="16">
+      <c r="A15" s="14">
         <v>3002</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="14">
         <v>3</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M15" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="K15" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="L15" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="M15" s="16" t="s">
+      <c r="N15" s="14">
+        <v>50</v>
+      </c>
+      <c r="O15" s="14" t="s">
         <v>76</v>
-      </c>
-      <c r="N15" s="16">
-        <v>50</v>
-      </c>
-      <c r="O15" s="16" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="16">
+      <c r="A16" s="14">
         <v>3003</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="14">
         <v>3</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M16" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="J16" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="K16" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="L16" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="N16" s="16">
+      <c r="N16" s="14">
         <v>50</v>
       </c>
-      <c r="O16" s="16" t="s">
-        <v>82</v>
+      <c r="O16" s="14" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="16">
+      <c r="A17" s="14">
         <v>3004</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="14">
         <v>3</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="J17" s="14"/>
+      <c r="K17" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L17" s="16">
+        <v>4999</v>
+      </c>
+      <c r="M17" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="I17" s="16"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="L17" s="18">
-        <v>4999</v>
-      </c>
-      <c r="M17" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16" t="s">
-        <v>84</v>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="16">
+      <c r="A18" s="14">
         <v>3005</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="14">
         <v>3</v>
       </c>
-      <c r="C18" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18" s="17" t="b">
+      <c r="C18" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="L18" s="18">
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="J18" s="14"/>
+      <c r="K18" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L18" s="16">
         <v>1999</v>
       </c>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16" t="s">
-        <v>86</v>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="16">
+      <c r="A19" s="14">
         <v>3006</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="14">
         <v>3</v>
       </c>
-      <c r="C19" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="17" t="b">
+      <c r="C19" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="L19" s="18">
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="J19" s="14"/>
+      <c r="K19" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="L19" s="16">
         <v>499</v>
       </c>
-      <c r="M19" s="16"/>
-      <c r="N19" s="16"/>
-      <c r="O19" s="16" t="s">
-        <v>53</v>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/shop.xlsx
+++ b/hall/resources/sample/shop.xlsx
@@ -331,7 +331,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="72">
   <si>
     <t>id</t>
   </si>
@@ -381,7 +381,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;int{_}int&gt;{;}</t>
+    <t>map&lt;int{_}int&gt;{|}</t>
   </si>
   <si>
     <t>bool</t>
@@ -390,7 +390,7 @@
     <t>Date&lt;yyyy-MM-dd HH:mm:ss&gt;</t>
   </si>
   <si>
-    <t>map&lt;int{_}long&gt;{;}</t>
+    <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
     <t>String</t>
@@ -441,12 +441,15 @@
     <t>1_10</t>
   </si>
   <si>
+    <t>2025-9-17 00:00:00</t>
+  </si>
+  <si>
+    <t>2025-10-25 23:59:59</t>
+  </si>
+  <si>
     <t>1022503_10</t>
   </si>
   <si>
-    <t>200</t>
-  </si>
-  <si>
     <t>sc_best value.png</t>
   </si>
   <si>
@@ -456,72 +459,39 @@
     <t>1_5</t>
   </si>
   <si>
-    <t>2025-9-17 00:00:00</t>
-  </si>
-  <si>
-    <t>2025-9-25 23:59:59</t>
-  </si>
-  <si>
     <t>1022503_5</t>
   </si>
   <si>
+    <t>sc_zhuanshi_icon6.png</t>
+  </si>
+  <si>
+    <t>1_1</t>
+  </si>
+  <si>
+    <t>1022503_1</t>
+  </si>
+  <si>
+    <t>sc_zhuanshi_icon1.png</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>1990000_30000000</t>
+  </si>
+  <si>
     <t>-1</t>
   </si>
   <si>
-    <t>499</t>
-  </si>
-  <si>
-    <t>sc_zhuanshi_icon6.png</t>
-  </si>
-  <si>
-    <t>1_1</t>
-  </si>
-  <si>
-    <t>2025-9-30 23:59:59</t>
-  </si>
-  <si>
-    <t>1022503_1</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>sc_zhuanshi_icon1.png</t>
-  </si>
-  <si>
-    <t>金币</t>
-  </si>
-  <si>
-    <t>1990000_20000000</t>
+    <t>1990000_13000000</t>
+  </si>
+  <si>
+    <t>sc_jinbi_icon5.png</t>
   </si>
   <si>
     <t>1990000_10000000</t>
   </si>
   <si>
-    <t>29999</t>
-  </si>
-  <si>
-    <t>1990000_16000000</t>
-  </si>
-  <si>
-    <t>1990000_8000000</t>
-  </si>
-  <si>
-    <t>12999</t>
-  </si>
-  <si>
-    <t>sc_jinbi_icon5.png</t>
-  </si>
-  <si>
-    <t>1990000_12000000</t>
-  </si>
-  <si>
-    <t>1990000_6000000</t>
-  </si>
-  <si>
-    <t>9999</t>
-  </si>
-  <si>
     <t>sc_jinbi_icon4.png</t>
   </si>
   <si>
@@ -531,13 +501,13 @@
     <t>sc_jinbi_icon3.png</t>
   </si>
   <si>
-    <t>1990000_4000000</t>
+    <t>1990000_2000000</t>
   </si>
   <si>
     <t>sc_jinbi_icon2.png</t>
   </si>
   <si>
-    <t>1990000_2000000</t>
+    <t>1990000_500000</t>
   </si>
   <si>
     <t>sc_jinbi_icon1.png</t>
@@ -546,28 +516,19 @@
     <t>钻石</t>
   </si>
   <si>
-    <t>1980000_20000</t>
-  </si>
-  <si>
-    <t>1980000_10000</t>
+    <t>1990000_30000</t>
   </si>
   <si>
     <t>sc_most popular.png</t>
   </si>
   <si>
-    <t>1980000_12000</t>
-  </si>
-  <si>
-    <t>1980000_8000</t>
+    <t>1990000_13000</t>
   </si>
   <si>
     <t>sc_zhuanshi_icon5.png</t>
   </si>
   <si>
-    <t>1980000_9000</t>
-  </si>
-  <si>
-    <t>1980000_6000</t>
+    <t>1990000_10000</t>
   </si>
   <si>
     <t>sc_zhuanshi_icon4.png</t>
@@ -579,13 +540,13 @@
     <t>sc_zhuanshi_icon3.png</t>
   </si>
   <si>
-    <t>1990000_3000</t>
+    <t>1990000_2000</t>
   </si>
   <si>
     <t>sc_zhuanshi_icon2.png</t>
   </si>
   <si>
-    <t>1990000_1000</t>
+    <t>1990000_500</t>
   </si>
 </sst>
 </file>
@@ -1770,26 +1731,30 @@
       <c r="F5" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
+      <c r="G5" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>37</v>
+      </c>
       <c r="I5" s="9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J5" s="10"/>
       <c r="K5" s="10">
         <v>1980000</v>
       </c>
-      <c r="L5" s="10" t="s">
-        <v>37</v>
+      <c r="L5" s="10">
+        <v>399</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N5" s="9">
         <v>100</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -1804,35 +1769,35 @@
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F6" s="9" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>43</v>
-      </c>
       <c r="J6" s="10"/>
-      <c r="K6" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>45</v>
+      <c r="K6" s="10">
+        <v>1980000</v>
+      </c>
+      <c r="L6" s="10">
+        <v>199</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N6" s="9">
         <v>50</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -1847,31 +1812,31 @@
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F7" s="9" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J7" s="10"/>
-      <c r="K7" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>50</v>
+      <c r="K7" s="10">
+        <v>1980000</v>
+      </c>
+      <c r="L7" s="10">
+        <v>39</v>
       </c>
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
       <c r="O7" s="9" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1882,11 +1847,11 @@
         <v>2</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F8" s="12" t="b">
         <v>1</v>
@@ -1894,25 +1859,21 @@
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
       <c r="I8" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>54</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="J8" s="13"/>
       <c r="K8" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8" s="13" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="L8" s="13">
+        <v>29999</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N8" s="11">
-        <v>100</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="N8" s="11"/>
       <c r="O8" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -1923,11 +1884,11 @@
         <v>2</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F9" s="12" t="b">
         <v>1</v>
@@ -1935,25 +1896,21 @@
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
       <c r="I9" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>57</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J9" s="13"/>
       <c r="K9" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>58</v>
+        <v>49</v>
+      </c>
+      <c r="L9" s="13">
+        <v>12999</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N9" s="11">
-        <v>100</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="N9" s="11"/>
       <c r="O9" s="11" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -1964,41 +1921,33 @@
         <v>2</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F10" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G10" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>42</v>
-      </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
       <c r="I10" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>61</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="J10" s="13"/>
       <c r="K10" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="L10" s="13" t="s">
-        <v>62</v>
+        <v>49</v>
+      </c>
+      <c r="L10" s="13">
+        <v>9999</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N10" s="11">
-        <v>100</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="N10" s="11"/>
       <c r="O10" s="11" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -2009,41 +1958,33 @@
         <v>2</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F11" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G11" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>48</v>
-      </c>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
       <c r="I11" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="13" t="s">
-        <v>64</v>
-      </c>
+      <c r="J11" s="13"/>
       <c r="K11" s="13" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L11" s="13">
         <v>4999</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N11" s="11">
-        <v>100</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="N11" s="11"/>
       <c r="O11" s="11" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -2054,11 +1995,11 @@
         <v>2</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F12" s="12" t="b">
         <v>1</v>
@@ -2066,25 +2007,21 @@
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
       <c r="I12" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>66</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="J12" s="13"/>
       <c r="K12" s="13" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L12" s="13">
         <v>1999</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N12" s="11">
-        <v>100</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="N12" s="11"/>
       <c r="O12" s="11" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -2095,11 +2032,11 @@
         <v>2</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="11" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F13" s="12" t="b">
         <v>1</v>
@@ -2107,25 +2044,21 @@
       <c r="G13" s="13"/>
       <c r="H13" s="13"/>
       <c r="I13" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>68</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="J13" s="13"/>
       <c r="K13" s="13" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L13" s="13">
         <v>499</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N13" s="11">
-        <v>100</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="N13" s="11"/>
       <c r="O13" s="11" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -2136,11 +2069,11 @@
         <v>3</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F14" s="15" t="b">
         <v>1</v>
@@ -2148,25 +2081,21 @@
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
       <c r="I14" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="J14" s="16" t="s">
-        <v>72</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="J14" s="16"/>
       <c r="K14" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="L14" s="16" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="L14" s="16">
+        <v>29999</v>
       </c>
       <c r="M14" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="N14" s="14">
-        <v>100</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="N14" s="14"/>
       <c r="O14" s="14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -2177,11 +2106,11 @@
         <v>3</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F15" s="15" t="b">
         <v>1</v>
@@ -2189,25 +2118,21 @@
       <c r="G15" s="16"/>
       <c r="H15" s="16"/>
       <c r="I15" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>75</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="J15" s="16"/>
       <c r="K15" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="L15" s="16" t="s">
-        <v>58</v>
+        <v>49</v>
+      </c>
+      <c r="L15" s="16">
+        <v>12999</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="N15" s="14">
-        <v>50</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="N15" s="14"/>
       <c r="O15" s="14" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -2218,41 +2143,33 @@
         <v>3</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F16" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="G16" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>42</v>
-      </c>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
       <c r="I16" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="J16" s="16" t="s">
-        <v>78</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="J16" s="16"/>
       <c r="K16" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="L16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16">
+        <v>9999</v>
+      </c>
+      <c r="M16" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="M16" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="N16" s="14">
-        <v>50</v>
-      </c>
+      <c r="N16" s="14"/>
       <c r="O16" s="14" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -2263,37 +2180,33 @@
         <v>3</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F17" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="G17" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>48</v>
-      </c>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
       <c r="I17" s="14" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="J17" s="14"/>
       <c r="K17" s="16" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L17" s="16">
         <v>4999</v>
       </c>
       <c r="M17" s="14" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="N17" s="14"/>
       <c r="O17" s="14" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:15">
@@ -2304,11 +2217,11 @@
         <v>3</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F18" s="15" t="b">
         <v>1</v>
@@ -2316,11 +2229,11 @@
       <c r="G18" s="16"/>
       <c r="H18" s="16"/>
       <c r="I18" s="14" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="J18" s="14"/>
       <c r="K18" s="16" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L18" s="16">
         <v>1999</v>
@@ -2328,7 +2241,7 @@
       <c r="M18" s="14"/>
       <c r="N18" s="14"/>
       <c r="O18" s="14" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -2339,11 +2252,11 @@
         <v>3</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F19" s="15" t="b">
         <v>1</v>
@@ -2351,11 +2264,11 @@
       <c r="G19" s="16"/>
       <c r="H19" s="16"/>
       <c r="I19" s="14" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="J19" s="14"/>
       <c r="K19" s="16" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L19" s="16">
         <v>499</v>
@@ -2363,7 +2276,7 @@
       <c r="M19" s="14"/>
       <c r="N19" s="14"/>
       <c r="O19" s="14" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/shop.xlsx
+++ b/hall/resources/sample/shop.xlsx
@@ -79,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -103,7 +103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -122,28 +122,6 @@
           </rPr>
           <t xml:space="preserve">
 不配置时间，表示永久存在</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-不配置表示永久存在</t>
         </r>
       </text>
     </comment>
@@ -165,8 +143,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-购买成功获得道具数量：
-金币充值和钻石充值 仅配置 金币和钻石，不配置其它道具 UI不支持</t>
+不配置表示永久存在</t>
         </r>
       </text>
     </comment>
@@ -188,7 +165,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-仅显示用：用在金币和钻石充值；其它类型不配置 UI暂不支持</t>
+购买成功获得道具数量：
+金币充值和钻石充值 仅配置 金币和钻石，不配置其它道具 UI不支持</t>
         </r>
       </text>
     </comment>
@@ -210,30 +188,30 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+仅显示用：用在金币和钻石充值；其它类型不配置 UI暂不支持</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 值=-1：充值类
 值&gt;-1：兑换类</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-“超值\划算”标签名称，可以不配置 则不显示</t>
         </r>
       </text>
     </comment>
@@ -255,8 +233,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-“XX% SALL”标签,可以不配置 不显示
-注：XX = 百分比数值</t>
+“超值\划算”标签名称，可以不配置 则不显示</t>
         </r>
       </text>
     </comment>
@@ -278,11 +255,34 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-底图中的大ICON图标</t>
+“XX% SALL”标签,可以不配置 不显示
+注：XX = 百分比数值</t>
         </r>
       </text>
     </comment>
-    <comment ref="O5" authorId="0">
+    <comment ref="P1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+底图中的大ICON图标</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -304,7 +304,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O8" authorId="0">
+    <comment ref="P8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -331,7 +331,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="89">
   <si>
     <t>id</t>
   </si>
@@ -348,6 +348,9 @@
     <t>解锁条件</t>
   </si>
   <si>
+    <t>等级显示条件</t>
+  </si>
+  <si>
     <t>是否开启</t>
   </si>
   <si>
@@ -405,6 +408,9 @@
     <t>level</t>
   </si>
   <si>
+    <t>grade</t>
+  </si>
+  <si>
     <t>open</t>
   </si>
   <si>
@@ -441,6 +447,9 @@
     <t>1_10</t>
   </si>
   <si>
+    <t>1_20</t>
+  </si>
+  <si>
     <t>2025-9-17 00:00:00</t>
   </si>
   <si>
@@ -459,6 +468,9 @@
     <t>1_5</t>
   </si>
   <si>
+    <t>20_30</t>
+  </si>
+  <si>
     <t>1022503_5</t>
   </si>
   <si>
@@ -468,6 +480,9 @@
     <t>1_1</t>
   </si>
   <si>
+    <t>30_40</t>
+  </si>
+  <si>
     <t>1022503_1</t>
   </si>
   <si>
@@ -477,36 +492,54 @@
     <t>金币</t>
   </si>
   <si>
+    <t>40_50</t>
+  </si>
+  <si>
     <t>1990000_30000000</t>
   </si>
   <si>
     <t>-1</t>
   </si>
   <si>
+    <t>50_60</t>
+  </si>
+  <si>
     <t>1990000_13000000</t>
   </si>
   <si>
     <t>sc_jinbi_icon5.png</t>
   </si>
   <si>
+    <t>60_80</t>
+  </si>
+  <si>
     <t>1990000_10000000</t>
   </si>
   <si>
     <t>sc_jinbi_icon4.png</t>
   </si>
   <si>
+    <t>80_100</t>
+  </si>
+  <si>
     <t>1990000_5000000</t>
   </si>
   <si>
     <t>sc_jinbi_icon3.png</t>
   </si>
   <si>
+    <t>100_120</t>
+  </si>
+  <si>
     <t>1990000_2000000</t>
   </si>
   <si>
     <t>sc_jinbi_icon2.png</t>
   </si>
   <si>
+    <t>120_130</t>
+  </si>
+  <si>
     <t>1990000_500000</t>
   </si>
   <si>
@@ -516,34 +549,52 @@
     <t>钻石</t>
   </si>
   <si>
+    <t>130_140</t>
+  </si>
+  <si>
     <t>1990000_30000</t>
   </si>
   <si>
     <t>sc_most popular.png</t>
   </si>
   <si>
+    <t>140_150</t>
+  </si>
+  <si>
     <t>1990000_13000</t>
   </si>
   <si>
     <t>sc_zhuanshi_icon5.png</t>
   </si>
   <si>
+    <t>150_160</t>
+  </si>
+  <si>
     <t>1990000_10000</t>
   </si>
   <si>
     <t>sc_zhuanshi_icon4.png</t>
   </si>
   <si>
+    <t>160_170</t>
+  </si>
+  <si>
     <t>1990000_5000</t>
   </si>
   <si>
     <t>sc_zhuanshi_icon3.png</t>
   </si>
   <si>
+    <t>170_180</t>
+  </si>
+  <si>
     <t>1990000_2000</t>
   </si>
   <si>
     <t>sc_zhuanshi_icon2.png</t>
+  </si>
+  <si>
+    <t>180_200</t>
   </si>
   <si>
     <t>1990000_500</t>
@@ -1559,27 +1610,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="5.5" style="1" customWidth="1"/>
     <col min="3" max="4" width="6.375" style="1" customWidth="1"/>
     <col min="5" max="5" width="17.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="30.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="28.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="19.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="20.125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="9.25" style="2" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="21.625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="6.875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="23.25" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="14.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="30.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="28.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="19.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="20.125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="9.25" style="2" customWidth="1"/>
+    <col min="13" max="13" width="8.875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="21.625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="6.875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="23.25" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1598,16 +1650,16 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="6" t="s">
@@ -1616,105 +1668,114 @@
       <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="6" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="7"/>
       <c r="E2" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="5" t="s">
         <v>18</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>19</v>
       </c>
+      <c r="J2" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="K2" s="8" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="G3" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="H3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>28</v>
       </c>
+      <c r="J3" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="K3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="5" t="s">
         <v>31</v>
       </c>
+      <c r="M3" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="N3" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:16">
       <c r="A5" s="9">
         <v>1001</v>
       </c>
@@ -1722,42 +1783,45 @@
         <v>1</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="9" t="b">
+        <v>37</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="H5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10">
+        <v>39</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10">
         <v>1980000</v>
       </c>
-      <c r="L5" s="10">
+      <c r="M5" s="10">
         <v>399</v>
       </c>
-      <c r="M5" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="9">
+      <c r="N5" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="9">
         <v>100</v>
       </c>
-      <c r="O5" s="9" t="s">
-        <v>40</v>
+      <c r="P5" s="9" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:16">
       <c r="A6" s="9">
         <v>1002</v>
       </c>
@@ -1765,42 +1829,45 @@
         <v>1</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="9" t="b">
+        <v>44</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="H6" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10">
+        <v>1980000</v>
+      </c>
+      <c r="M6" s="10">
+        <v>199</v>
+      </c>
+      <c r="N6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10">
-        <v>1980000</v>
-      </c>
-      <c r="L6" s="10">
-        <v>199</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6" s="9">
+      <c r="O6" s="9">
         <v>50</v>
       </c>
-      <c r="O6" s="9" t="s">
-        <v>43</v>
+      <c r="P6" s="9" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:16">
       <c r="A7" s="9">
         <v>1003</v>
       </c>
@@ -1808,38 +1875,41 @@
         <v>1</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="9" t="b">
+        <v>48</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="H7" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10">
+        <v>39</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10">
         <v>1980000</v>
       </c>
-      <c r="L7" s="10">
+      <c r="M7" s="10">
         <v>39</v>
       </c>
-      <c r="M7" s="9"/>
       <c r="N7" s="9"/>
-      <c r="O7" s="9" t="s">
-        <v>46</v>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:16">
       <c r="A8" s="11">
         <v>2001</v>
       </c>
@@ -1847,36 +1917,39 @@
         <v>2</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="12" t="b">
+        <v>48</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G8" s="13"/>
       <c r="H8" s="13"/>
-      <c r="I8" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="L8" s="13">
+      <c r="I8" s="13"/>
+      <c r="J8" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="13">
         <v>29999</v>
       </c>
-      <c r="M8" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N8" s="11"/>
-      <c r="O8" s="11" t="s">
-        <v>40</v>
+      <c r="N8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:16">
       <c r="A9" s="11">
         <v>2002</v>
       </c>
@@ -1884,36 +1957,39 @@
         <v>2</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="12" t="b">
+        <v>48</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G9" s="13"/>
       <c r="H9" s="13"/>
-      <c r="I9" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="L9" s="13">
+      <c r="I9" s="13"/>
+      <c r="J9" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9" s="13">
         <v>12999</v>
       </c>
-      <c r="M9" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N9" s="11"/>
-      <c r="O9" s="11" t="s">
-        <v>51</v>
+      <c r="N9" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:16">
       <c r="A10" s="11">
         <v>2003</v>
       </c>
@@ -1921,36 +1997,39 @@
         <v>2</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="12" t="b">
+        <v>48</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G10" s="13"/>
       <c r="H10" s="13"/>
-      <c r="I10" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="L10" s="13">
+      <c r="I10" s="13"/>
+      <c r="J10" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" s="13">
         <v>9999</v>
       </c>
-      <c r="M10" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11" t="s">
-        <v>53</v>
+      <c r="N10" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:16">
       <c r="A11" s="11">
         <v>2004</v>
       </c>
@@ -1958,36 +2037,39 @@
         <v>2</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="12" t="b">
+        <v>48</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G11" s="13"/>
       <c r="H11" s="13"/>
-      <c r="I11" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="L11" s="13">
+      <c r="I11" s="13"/>
+      <c r="J11" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="M11" s="13">
         <v>4999</v>
       </c>
-      <c r="M11" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11" t="s">
-        <v>55</v>
+      <c r="N11" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:16">
       <c r="A12" s="11">
         <v>2005</v>
       </c>
@@ -1995,36 +2077,39 @@
         <v>2</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F12" s="12" t="b">
+        <v>48</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G12" s="13"/>
       <c r="H12" s="13"/>
-      <c r="I12" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="L12" s="13">
+      <c r="I12" s="13"/>
+      <c r="J12" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="M12" s="13">
         <v>1999</v>
       </c>
-      <c r="M12" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11" t="s">
-        <v>57</v>
+      <c r="N12" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O12" s="11"/>
+      <c r="P12" s="11" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:16">
       <c r="A13" s="11">
         <v>2006</v>
       </c>
@@ -2032,36 +2117,39 @@
         <v>2</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="12" t="b">
+        <v>48</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G13" s="13"/>
       <c r="H13" s="13"/>
-      <c r="I13" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="L13" s="13">
+      <c r="I13" s="13"/>
+      <c r="J13" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="M13" s="13">
         <v>499</v>
       </c>
-      <c r="M13" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11" t="s">
-        <v>59</v>
+      <c r="N13" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:16">
       <c r="A14" s="14">
         <v>3001</v>
       </c>
@@ -2069,36 +2157,39 @@
         <v>3</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="15" t="b">
+        <v>48</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="G14" s="16"/>
       <c r="H14" s="16"/>
-      <c r="I14" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L14" s="16">
+      <c r="I14" s="16"/>
+      <c r="J14" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M14" s="16">
         <v>29999</v>
       </c>
-      <c r="M14" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14" t="s">
-        <v>43</v>
+      <c r="N14" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="O14" s="14"/>
+      <c r="P14" s="14" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:16">
       <c r="A15" s="14">
         <v>3002</v>
       </c>
@@ -2106,36 +2197,39 @@
         <v>3</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="15" t="b">
+        <v>48</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="G15" s="16"/>
       <c r="H15" s="16"/>
-      <c r="I15" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L15" s="16">
+      <c r="I15" s="16"/>
+      <c r="J15" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15" s="16">
         <v>12999</v>
       </c>
-      <c r="M15" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14" t="s">
-        <v>64</v>
+      <c r="N15" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="O15" s="14"/>
+      <c r="P15" s="14" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:16">
       <c r="A16" s="14">
         <v>3003</v>
       </c>
@@ -2143,36 +2237,39 @@
         <v>3</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="15" t="b">
+        <v>48</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="G16" s="16"/>
       <c r="H16" s="16"/>
-      <c r="I16" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L16" s="16">
+      <c r="I16" s="16"/>
+      <c r="J16" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16" s="16">
         <v>9999</v>
       </c>
-      <c r="M16" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14" t="s">
-        <v>66</v>
+      <c r="N16" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="O16" s="14"/>
+      <c r="P16" s="14" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:16">
       <c r="A17" s="14">
         <v>3004</v>
       </c>
@@ -2180,36 +2277,39 @@
         <v>3</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F17" s="15" t="b">
+        <v>48</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="G17" s="16"/>
       <c r="H17" s="16"/>
-      <c r="I17" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="J17" s="14"/>
-      <c r="K17" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L17" s="16">
+      <c r="I17" s="16"/>
+      <c r="J17" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="K17" s="14"/>
+      <c r="L17" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M17" s="16">
         <v>4999</v>
       </c>
-      <c r="M17" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14" t="s">
-        <v>68</v>
+      <c r="N17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:16">
       <c r="A18" s="14">
         <v>3005</v>
       </c>
@@ -2217,34 +2317,37 @@
         <v>3</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" s="15" t="b">
+        <v>48</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="G18" s="16"/>
       <c r="H18" s="16"/>
-      <c r="I18" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="J18" s="14"/>
-      <c r="K18" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L18" s="16">
+      <c r="I18" s="16"/>
+      <c r="J18" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="K18" s="14"/>
+      <c r="L18" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M18" s="16">
         <v>1999</v>
       </c>
-      <c r="M18" s="14"/>
       <c r="N18" s="14"/>
-      <c r="O18" s="14" t="s">
-        <v>70</v>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:16">
       <c r="A19" s="14">
         <v>3006</v>
       </c>
@@ -2252,31 +2355,34 @@
         <v>3</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" s="15" t="b">
+        <v>48</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="G19" s="16"/>
       <c r="H19" s="16"/>
-      <c r="I19" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="J19" s="14"/>
-      <c r="K19" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L19" s="16">
+      <c r="I19" s="16"/>
+      <c r="J19" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="K19" s="14"/>
+      <c r="L19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M19" s="16">
         <v>499</v>
       </c>
-      <c r="M19" s="14"/>
       <c r="N19" s="14"/>
-      <c r="O19" s="14" t="s">
-        <v>46</v>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
